--- a/docs/02-功能测试用例表.xlsx
+++ b/docs/02-功能测试用例表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MoodBoard-Complete\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6491D1A-B458-4F6F-A5BB-846C7084F0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="20152" windowHeight="8955"/>
+    <workbookView xWindow="5805" yWindow="532" windowWidth="11572" windowHeight="12466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="功能测试用例" sheetId="1" r:id="rId1"/>
@@ -12,25 +18,13 @@
     <sheet name="下拉选项" sheetId="3" r:id="rId3"/>
     <sheet name="Bug记录模板" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="585">
   <si>
     <t>用例ID</t>
   </si>
@@ -111,6 +105,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中保存</t>
@@ -165,6 +160,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>账号或密码错误</t>
@@ -181,6 +177,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，不跳转</t>
@@ -347,6 +344,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>注册切换正常，游客登录仅在登录模式显示，布局不变形</t>
@@ -474,6 +472,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>个日期卡片</t>
@@ -616,6 +615,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>或主情绪与情绪列表</t>
@@ -654,6 +654,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>被取消</t>
@@ -793,6 +794,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>杭州市</t>
@@ -809,6 +811,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>临平区</t>
@@ -825,6 +828,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，下方显示经纬度</t>
@@ -888,6 +892,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>当前位置</t>
@@ -904,6 +909,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>或明确错误提示</t>
@@ -925,6 +931,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>当前位置</t>
@@ -965,6 +972,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、正文、关键词、图片、位置均正确回显</t>
@@ -2180,18 +2188,52 @@
   <si>
     <t>BUG-005</t>
   </si>
+  <si>
+    <t>点击清空会话后，右侧聊天内容清空，但左侧会话标题仍显示原聊天内容</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-003</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>左侧 session title / preview 未同步更新</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>列1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC-AI-新增AI树洞-会话管理</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除单个历史会话</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 进入日常树洞；2. 新建多个会话；3. 在左侧会话栏尝试删除某个会话</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以删除指定会话，删除后该会话不再显示</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>左侧会话栏没有删除入口</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-004</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2225,161 +2267,21 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2398,194 +2300,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2593,340 +2309,68 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFECACA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2940,55 +2384,158 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
+          <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFECACA"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFE0E7FF"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2999,7 +2546,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -3027,206 +2574,93 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="11"/>
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstColumn" dxfId="8"/>
-      <tableStyleElement type="lastColumn" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstColumn" dxfId="18"/>
+      <tableStyleElement type="lastColumn" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="18"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="17"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="15"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="14"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="13"/>
-      <tableStyleElement type="pageFieldValues" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="totalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="10"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="8"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="7"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="6"/>
+      <tableStyleElement type="pageFieldValues" dxfId="5"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FunctionalTestCases" displayName="FunctionalTestCases" ref="A1:L82">
-  <tableColumns count="12">
-    <tableColumn id="1" name="用例ID"/>
-    <tableColumn id="2" name="模块"/>
-    <tableColumn id="3" name="功能点"/>
-    <tableColumn id="4" name="优先级"/>
-    <tableColumn id="5" name="用例标题"/>
-    <tableColumn id="6" name="前置条件"/>
-    <tableColumn id="7" name="测试步骤"/>
-    <tableColumn id="8" name="测试数据"/>
-    <tableColumn id="9" name="预期结果"/>
-    <tableColumn id="10" name="实际结果"/>
-    <tableColumn id="11" name="执行状态"/>
-    <tableColumn id="12" name="缺陷编号/备注"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FunctionalTestCases" displayName="FunctionalTestCases" ref="A1:M83">
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="用例ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="模块"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="功能点"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="优先级"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="用例标题"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="前置条件"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="测试步骤"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="测试数据"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="预期结果"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="实际结果"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="执行状态"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="缺陷编号/备注"/>
+    <tableColumn id="13" xr3:uid="{A23D8921-B8EE-428C-B4A9-FA2A65009F6A}" name="列1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SummaryTable" displayName="SummaryTable" ref="A2:D11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SummaryTable" displayName="SummaryTable" ref="A2:D11">
   <tableColumns count="4">
-    <tableColumn id="1" name="统计项"/>
-    <tableColumn id="2" name="数量"/>
-    <tableColumn id="3" name="说明"/>
-    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="统计项"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="数量"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BugTemplateTable" displayName="BugTemplateTable" ref="A1:L6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="BugTemplateTable" displayName="BugTemplateTable" ref="A1:L6">
   <tableColumns count="12">
-    <tableColumn id="1" name="缺陷编号"/>
-    <tableColumn id="2" name="所属模块"/>
-    <tableColumn id="3" name="关联用例ID"/>
-    <tableColumn id="4" name="缺陷标题"/>
-    <tableColumn id="5" name="严重程度"/>
-    <tableColumn id="6" name="优先级"/>
-    <tableColumn id="7" name="复现步骤"/>
-    <tableColumn id="8" name="预期结果"/>
-    <tableColumn id="9" name="实际结果"/>
-    <tableColumn id="10" name="状态"/>
-    <tableColumn id="11" name="负责人"/>
-    <tableColumn id="12" name="备注"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="缺陷编号"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="所属模块"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="关联用例ID"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="缺陷标题"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="严重程度"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="优先级"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="复现步骤"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="预期结果"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="实际结果"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="状态"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="负责人"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="备注"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3375,13 +2809,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3397,7 +2831,7 @@
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12">
+    <row r="1" spans="1:13" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3434,3127 +2868,3168 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" ht="60" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="M1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="60" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="L2" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="60" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1" spans="1:12">
-      <c r="A4" s="8" t="s">
+      <c r="K3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="60" customHeight="1">
+      <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1" spans="1:12">
-      <c r="A5" s="8" t="s">
+      <c r="K4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="60" customHeight="1">
+      <c r="A5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1" spans="1:12">
-      <c r="A6" s="8" t="s">
+      <c r="K5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="60" customHeight="1">
+      <c r="A6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1" spans="1:12">
-      <c r="A7" s="8" t="s">
+      <c r="K6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="60" customHeight="1">
+      <c r="A7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1" spans="1:12">
-      <c r="A8" s="8" t="s">
+      <c r="K7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="60" customHeight="1">
+      <c r="A8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1" spans="1:12">
-      <c r="A9" s="8" t="s">
+      <c r="K8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="60" customHeight="1">
+      <c r="A9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1" spans="1:12">
-      <c r="A10" s="8" t="s">
+      <c r="K9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="60" customHeight="1">
+      <c r="A10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1" spans="1:12">
-      <c r="A11" s="8" t="s">
+      <c r="K10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="60" customHeight="1">
+      <c r="A11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1" spans="1:12">
-      <c r="A12" s="8" t="s">
+      <c r="K11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="60" customHeight="1">
+      <c r="A12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1" spans="1:12">
-      <c r="A13" s="8" t="s">
+      <c r="K12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="60" customHeight="1">
+      <c r="A13" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1" spans="1:12">
-      <c r="A14" s="8" t="s">
+      <c r="K13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="60" customHeight="1">
+      <c r="A14" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1" spans="1:12">
-      <c r="A15" s="8" t="s">
+      <c r="K14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="60" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1" spans="1:12">
-      <c r="A16" s="8" t="s">
+      <c r="K15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="60" customHeight="1">
+      <c r="A16" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1" spans="1:12">
-      <c r="A17" s="8" t="s">
+      <c r="K16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="60" customHeight="1">
+      <c r="A17" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1" spans="1:12">
-      <c r="A18" s="8" t="s">
+      <c r="K17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="60" customHeight="1">
+      <c r="A18" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1" spans="1:12">
-      <c r="A19" s="8" t="s">
+      <c r="K18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="60" customHeight="1">
+      <c r="A19" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1" spans="1:12">
-      <c r="A20" s="8" t="s">
+      <c r="K19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="60" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1" spans="1:12">
-      <c r="A21" s="8" t="s">
+      <c r="K20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="60" customHeight="1">
+      <c r="A21" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1" spans="1:12">
-      <c r="A22" s="8" t="s">
+      <c r="K21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="60" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1" spans="1:12">
-      <c r="A23" s="8" t="s">
+      <c r="K22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="60" customHeight="1">
+      <c r="A23" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1" spans="1:12">
-      <c r="A24" s="8" t="s">
+      <c r="K23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="60" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1" spans="1:12">
-      <c r="A25" s="8" t="s">
+      <c r="J24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="60" customHeight="1">
+      <c r="A25" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1" spans="1:12">
-      <c r="A26" s="8" t="s">
+      <c r="J25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="60" customHeight="1">
+      <c r="A26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="K26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L26" s="8" t="s">
+      <c r="K26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" spans="1:12">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:12" ht="60" customHeight="1">
+      <c r="A27" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1" spans="1:12">
-      <c r="A28" s="8" t="s">
+      <c r="K27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="60" customHeight="1">
+      <c r="A28" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="K28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" s="8"/>
-    </row>
-    <row r="29" ht="60" customHeight="1" spans="1:12">
-      <c r="A29" s="8" t="s">
+      <c r="K28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L28" s="7"/>
+    </row>
+    <row r="29" spans="1:12" ht="60" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="K29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1" spans="1:12">
-      <c r="A30" s="8" t="s">
+      <c r="K29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="60" customHeight="1">
+      <c r="A30" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1" spans="1:12">
-      <c r="A31" s="8" t="s">
+      <c r="J30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="60" customHeight="1">
+      <c r="A31" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="J31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1" spans="1:12">
-      <c r="A32" s="8" t="s">
+      <c r="J31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="60" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="J32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1" spans="1:12">
-      <c r="A33" s="8" t="s">
+      <c r="J32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="60" customHeight="1">
+      <c r="A33" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="J33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1" spans="1:12">
-      <c r="A34" s="8" t="s">
+      <c r="J33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="60" customHeight="1">
+      <c r="A34" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="J34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1" spans="1:12">
-      <c r="A35" s="8" t="s">
+      <c r="J34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="60" customHeight="1">
+      <c r="A35" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="J35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1" spans="1:12">
-      <c r="A36" s="8" t="s">
+      <c r="J35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="60" customHeight="1">
+      <c r="A36" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="J36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1" spans="1:12">
-      <c r="A37" s="8" t="s">
+      <c r="J36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="60" customHeight="1">
+      <c r="A37" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="J37" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1" spans="1:12">
-      <c r="A38" s="8" t="s">
+      <c r="J37" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="M37" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="60" customHeight="1">
+      <c r="A38" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="J38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1" spans="1:12">
-      <c r="A39" s="8" t="s">
+      <c r="J38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="60" customHeight="1">
+      <c r="A39" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="J39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1" spans="1:12">
-      <c r="A40" s="8" t="s">
+      <c r="J39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="60" customHeight="1">
+      <c r="A40" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="J40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1" spans="1:12">
-      <c r="A41" s="8" t="s">
+      <c r="J40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="60" customHeight="1">
+      <c r="A41" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="I41" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="J41" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" ht="60" customHeight="1" spans="1:12">
-      <c r="A42" s="8" t="s">
+      <c r="J41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="60" customHeight="1">
+      <c r="A42" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="J42" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1" spans="1:12">
-      <c r="A43" s="8" t="s">
+      <c r="J42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="60" customHeight="1">
+      <c r="A43" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="I43" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="J43" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1" spans="1:12">
-      <c r="A44" s="8" t="s">
+      <c r="J43" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="60" customHeight="1">
+      <c r="A44" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="I44" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="J44" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1" spans="1:12">
-      <c r="A45" s="8" t="s">
+      <c r="J44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="60" customHeight="1">
+      <c r="A45" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I45" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="J45" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L45" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1" spans="1:12">
-      <c r="A46" s="8" t="s">
+      <c r="J45" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="60" customHeight="1">
+      <c r="A46" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="I46" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="J46" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L46" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" ht="60" customHeight="1" spans="1:12">
-      <c r="A47" s="8" t="s">
+      <c r="J46" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="60" customHeight="1">
+      <c r="A47" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="I47" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="J47" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L47" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" ht="60" customHeight="1" spans="1:12">
-      <c r="A48" s="8" t="s">
+      <c r="J47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="60" customHeight="1">
+      <c r="A48" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I48" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="J48" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1" spans="1:12">
-      <c r="A49" s="8" t="s">
+      <c r="J48" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="60" customHeight="1">
+      <c r="A49" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="I49" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="J49" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" ht="60" customHeight="1" spans="1:12">
-      <c r="A50" s="8" t="s">
+      <c r="J49" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="60" customHeight="1">
+      <c r="A50" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="I50" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="J50" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1" spans="1:12">
-      <c r="A51" s="8" t="s">
+      <c r="J50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="60" customHeight="1">
+      <c r="A51" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="I51" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="J51" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L51" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1" spans="1:12">
-      <c r="A52" s="8" t="s">
+      <c r="J51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="60" customHeight="1">
+      <c r="A52" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="J52" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1" spans="1:12">
-      <c r="A53" s="8" t="s">
+      <c r="J52" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="60" customHeight="1">
+      <c r="A53" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="I53" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="J53" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L53" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1" spans="1:12">
-      <c r="A54" s="8" t="s">
+      <c r="J53" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="60" customHeight="1">
+      <c r="A54" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="I54" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="J54" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L54" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" ht="60" customHeight="1" spans="1:12">
-      <c r="A55" s="8" t="s">
+      <c r="J54" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="60" customHeight="1">
+      <c r="A55" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="I55" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="J55" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1" spans="1:12">
-      <c r="A56" s="8" t="s">
+      <c r="J55" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="60" customHeight="1">
+      <c r="A56" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="J56" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1" spans="1:12">
-      <c r="A57" s="8" t="s">
+      <c r="J56" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="60" customHeight="1">
+      <c r="A57" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F57" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I57" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="J57" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1" spans="1:12">
-      <c r="A58" s="8" t="s">
+      <c r="J57" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="60" customHeight="1">
+      <c r="A58" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F58" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="I58" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="J58" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" ht="60" customHeight="1" spans="1:12">
-      <c r="A59" s="8" t="s">
+      <c r="J58" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="60" customHeight="1">
+      <c r="A59" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="F59" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="H59" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="I59" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="J59" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" ht="60" customHeight="1" spans="1:12">
-      <c r="A60" s="8" t="s">
+      <c r="J59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="60" customHeight="1">
+      <c r="A60" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="I60" s="8" t="s">
+      <c r="I60" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="J60" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L60" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" ht="60" customHeight="1" spans="1:12">
-      <c r="A61" s="8" t="s">
+      <c r="J60" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="60" customHeight="1">
+      <c r="A61" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="I61" s="8" t="s">
+      <c r="I61" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="J61" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K61" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L61" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" ht="60" customHeight="1" spans="1:12">
-      <c r="A62" s="8" t="s">
+      <c r="J61" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="60" customHeight="1">
+      <c r="A62" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="F62" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="H62" s="8" t="s">
+      <c r="H62" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="I62" s="8" t="s">
+      <c r="I62" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="J62" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K62" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L62" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" ht="60" customHeight="1" spans="1:12">
-      <c r="A63" s="8" t="s">
+      <c r="J62" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="60" customHeight="1">
+      <c r="A63" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="I63" s="8" t="s">
+      <c r="I63" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="J63" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" ht="60" customHeight="1" spans="1:12">
-      <c r="A64" s="8" t="s">
+      <c r="J63" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="60" customHeight="1">
+      <c r="A64" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F64" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="I64" s="8" t="s">
+      <c r="I64" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="J64" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L64" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" ht="60" customHeight="1" spans="1:12">
-      <c r="A65" s="8" t="s">
+      <c r="J64" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="60" customHeight="1">
+      <c r="A65" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="F65" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="I65" s="8" t="s">
+      <c r="I65" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="J65" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K65" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L65" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1" spans="1:12">
-      <c r="A66" s="8" t="s">
+      <c r="J65" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="60" customHeight="1">
+      <c r="A66" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="F66" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="H66" s="8" t="s">
+      <c r="H66" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="I66" s="8" t="s">
+      <c r="I66" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="J66" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L66" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1" spans="1:12">
-      <c r="A67" s="8" t="s">
+      <c r="J66" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="60" customHeight="1">
+      <c r="A67" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="H67" s="8" t="s">
+      <c r="H67" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I67" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="J67" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K67" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L67" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" ht="60" customHeight="1" spans="1:12">
-      <c r="A68" s="8" t="s">
+      <c r="J67" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="60" customHeight="1">
+      <c r="A68" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="H68" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="I68" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="J68" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K68" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L68" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" ht="60" customHeight="1" spans="1:12">
-      <c r="A69" s="8" t="s">
+      <c r="J68" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="60" customHeight="1">
+      <c r="A69" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="J69" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K69" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L69" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1" spans="1:12">
-      <c r="A70" s="8" t="s">
+      <c r="J69" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="60" customHeight="1">
+      <c r="A70" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="I70" s="8" t="s">
+      <c r="I70" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="J70" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K70" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L70" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1" spans="1:12">
-      <c r="A71" s="8" t="s">
+      <c r="J70" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="60" customHeight="1">
+      <c r="A71" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="H71" s="8" t="s">
+      <c r="H71" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="I71" s="8" t="s">
+      <c r="I71" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="J71" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K71" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L71" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" ht="60" customHeight="1" spans="1:12">
-      <c r="A72" s="8" t="s">
+      <c r="J71" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="60" customHeight="1">
+      <c r="A72" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="I72" s="8" t="s">
+      <c r="I72" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="J72" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K72" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L72" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" ht="60" customHeight="1" spans="1:12">
-      <c r="A73" s="8" t="s">
+      <c r="J72" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="60" customHeight="1">
+      <c r="A73" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G73" s="8" t="s">
+      <c r="G73" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="H73" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="I73" s="8" t="s">
+      <c r="I73" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="J73" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K73" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L73" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" ht="60" customHeight="1" spans="1:12">
-      <c r="A74" s="8" t="s">
+      <c r="J73" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="60" customHeight="1">
+      <c r="A74" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="I74" s="8" t="s">
+      <c r="I74" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="J74" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K74" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L74" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" ht="60" customHeight="1" spans="1:12">
-      <c r="A75" s="8" t="s">
+      <c r="J74" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="60" customHeight="1">
+      <c r="A75" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G75" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="I75" s="8" t="s">
+      <c r="I75" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="J75" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K75" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L75" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1" spans="1:12">
-      <c r="A76" s="8" t="s">
+      <c r="J75" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L75" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="60" customHeight="1">
+      <c r="A76" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="H76" s="8" t="s">
+      <c r="H76" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="I76" s="8" t="s">
+      <c r="I76" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="J76" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L76" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" ht="60" customHeight="1" spans="1:12">
-      <c r="A77" s="8" t="s">
+      <c r="J76" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="60" customHeight="1">
+      <c r="A77" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="G77" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="I77" s="8" t="s">
+      <c r="I77" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="J77" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K77" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L77" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" ht="60" customHeight="1" spans="1:12">
-      <c r="A78" s="8" t="s">
+      <c r="J77" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="60" customHeight="1">
+      <c r="A78" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="D78" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="G78" s="8" t="s">
+      <c r="G78" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="I78" s="8" t="s">
+      <c r="I78" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="J78" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K78" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L78" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" ht="60" customHeight="1" spans="1:12">
-      <c r="A79" s="8" t="s">
+      <c r="J78" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L78" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="60" customHeight="1">
+      <c r="A79" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="G79" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="I79" s="8" t="s">
+      <c r="I79" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="J79" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K79" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L79" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" ht="60" customHeight="1" spans="1:12">
-      <c r="A80" s="8" t="s">
+      <c r="J79" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="60" customHeight="1">
+      <c r="A80" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="F80" s="8" t="s">
+      <c r="F80" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="I80" s="8" t="s">
+      <c r="I80" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="J80" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K80" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L80" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" ht="60" customHeight="1" spans="1:12">
-      <c r="A81" s="8" t="s">
+      <c r="J80" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="60" customHeight="1">
+      <c r="A81" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="D81" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F81" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="I81" s="8" t="s">
+      <c r="I81" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="J81" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K81" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L81" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" ht="60" customHeight="1" spans="1:12">
-      <c r="A82" s="8" t="s">
+      <c r="J81" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="60" customHeight="1">
+      <c r="A82" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="F82" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="G82" s="8" t="s">
+      <c r="G82" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="I82" s="8" t="s">
+      <c r="I82" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="J82" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K82" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L82" s="8" t="s">
-        <v>22</v>
+      <c r="J82" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="34.5" customHeight="1">
+      <c r="A83" t="s">
+        <v>579</v>
+      </c>
+      <c r="C83" t="s">
+        <v>580</v>
+      </c>
+      <c r="G83" t="s">
+        <v>581</v>
+      </c>
+      <c r="I83" t="s">
+        <v>582</v>
+      </c>
+      <c r="J83" t="s">
+        <v>583</v>
+      </c>
+      <c r="K83" t="s">
+        <v>554</v>
+      </c>
+      <c r="L83" t="s">
+        <v>584</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D82">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="D2:D83">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$D2="P0"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$D2="P1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K82">
+  <conditionalFormatting sqref="K2:K83">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$K2="通过"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$K2="失败"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>$K2="阻塞"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="B2:B82">
-      <formula1>下拉选项!$A$2:$A$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D2:D82">
-      <formula1>下拉选项!$B$2:$B$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="K2:K82">
-      <formula1>下拉选项!$C$2:$C$6</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>下拉选项!$A$2:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B83</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>下拉选项!$B$2:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D83</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>下拉选项!$C$2:$C$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K83</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -6562,166 +6037,166 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:4">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="34.049999999999997" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" ht="13.85" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="B3" s="6">
-        <f>COUNTA(功能测试用例!A2:A82)</f>
-        <v>81</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="11">
+        <f>COUNTA(功能测试用例!A2:A83)</f>
+        <v>82</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="B4" s="6">
-        <f>COUNTIF(功能测试用例!D2:D82,"P0")</f>
-        <v>29</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="11">
+        <f>COUNTIF(功能测试用例!D2:D83,"P0")</f>
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B5" s="6">
-        <f>COUNTIF(功能测试用例!D2:D82,"P1")</f>
+      <c r="B5" s="11">
+        <f>COUNTIF(功能测试用例!D2:D83,"P1")</f>
         <v>37</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="B6" s="6">
-        <f>COUNTIF(功能测试用例!D2:D82,"P2")</f>
+      <c r="B6" s="11">
+        <f>COUNTIF(功能测试用例!D2:D83,"P2")</f>
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B7" s="6">
-        <f>COUNTIF(功能测试用例!K2:K82,"通过")</f>
+      <c r="B7" s="11">
+        <f>COUNTIF(功能测试用例!K2:K83,"通过")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B8" s="6">
-        <f>COUNTIF(功能测试用例!K2:K82,"失败")</f>
+      <c r="B8" s="11">
+        <f>COUNTIF(功能测试用例!K2:K83,"失败")</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B9" s="11">
+        <f>COUNTIF(功能测试用例!K2:K83,"阻塞")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="B9" s="6">
-        <f>COUNTIF(功能测试用例!K2:K82,"阻塞")</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="B10" s="6">
-        <f>COUNTIF(功能测试用例!K2:K82,"未执行")</f>
-        <v>80</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="11">
+        <f>COUNTIF(功能测试用例!K2:K83,"未执行")</f>
+        <v>79</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <f>IF(B3=0,0,B7/B3)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -6729,8 +6204,8 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -6738,15 +6213,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.85" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -6846,16 +6320,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
@@ -6867,7 +6340,7 @@
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.9" spans="1:12">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>557</v>
       </c>
@@ -7096,8 +6569,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
